--- a/stories/arbres/TREE-SAN-011.xlsx
+++ b/stories/arbres/TREE-SAN-011.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va au parc avec maman. Papa porte le panier. C'est l'heure de manger. On s'assoit. Assis à table, ensemble. Ici, la table est une nappe sur l'herbe. Sara pose les fesses. Elle reste assise.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Un chat passe au loin. Sara s'assoit sur la nappe. Les fesses posées. Papa s'assoit. Maman s'assoit. Ils mangent ensemble, à table, sur la nappe. Sara reste assise.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va manger au parc. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est assise. La nappe est leur table. Ensemble, c'est calme. Le chat s'éloigne.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2225,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2207,7 +2254,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sara a mangé assise, à table, ensemble. Puis elle va au bac. Elle reste calme. Maman dit : on a bien mangé assis.</t>
+          <t>Sara a mangé assise, à table, ensemble. Puis elle va au bac. Elle reste calme. On a bien mangé assis.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2345,6 +2392,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a mangé assise, à table, ensemble. Puis elle va au bac. Elle reste calme.
+maman|On a bien mangé assis.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|La nappe rouge est pliée. Sara a mangé assise à table, ensemble. Le bac l'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|La nappe bleue sent l'herbe. Sara était assise. Ensemble, à table.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|La nappe verte a une miette. Sara a mangé assise, ensemble, à table.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3531,7 +3619,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Après le repas, assise, Sara va au toboggan. Elle a mangé à table, ensemble. Papa dit : d'abord assis. Puis on glisse.</t>
+          <t>Après le repas, assise, Sara va au toboggan. Elle a mangé à table, ensemble. D'abord assis. Puis on glisse.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3669,6 +3757,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Après le repas, assise, Sara va au toboggan. Elle a mangé à table, ensemble.
+papa|D'abord assis.
+narrateur|Puis on glisse.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3952,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4121,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Puis le toboggan.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4288,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4455,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Elle glisse.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4622,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4789,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Le toboggan attend.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4956,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5123,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se balance après. Elle a d'abord mangé assise. À table, ensemble. Maman plie un coin de nappe.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5316,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5485,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. La balançoire craque.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5652,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5819,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Elle se balance.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5986,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6153,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Maman plie.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6320,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6317,6 +6487,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien du parc reste avec son maître, loin. Sara s'assoit. Fesses sur la nappe. Papa et maman s'assoient. Ils mangent ensemble à table. Sara tient son sandwich. Elle reste assise.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6668,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien est loin. Sara, elle, que fait-elle pour manger ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6841,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est assise. Le chien ne vient pas. À table, ensemble, c'est le pique-nique.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7036,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6875,7 +7065,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sara a mangé assise, ensemble, à table. Au bac, elle creuse. Papa dit : d'abord on était assis.</t>
+          <t>Sara a mangé assise, ensemble, à table. Au bac, elle creuse. D'abord on était assis.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7013,6 +7203,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a mangé assise, ensemble, à table. Au bac, elle creuse.
+papa|D'abord on était assis.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7397,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7566,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Le sable est tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7733,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7900,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Elle creuse.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8067,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8234,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Papa garde le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8401,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8568,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Au toboggan, Sara attend son tour. Elle a mangé assise à table, ensemble. Maman range le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8761,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8930,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Elle attend.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9097,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9264,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Le toboggan brille.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9431,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9598,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Maman range.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9765,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9932,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se balance. Elle a d'abord été assise. À table, ensemble. Papa pousse tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10125,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10294,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Ça va, ça vient.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10461,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10628,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Papa pousse.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10795,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10962,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Elle chante.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11129,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10985,6 +11296,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Une poule du jardin d'à côté picore loin. Sara s'assoit à table, sur la nappe. Ensemble. Papa verse de l'eau. Maman ouvre la boîte. Sara mange assise. Les fesses bien posées.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11161,6 +11477,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|La poule picore. Sara, elle, que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11329,6 +11650,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est assise. La poule reste loin. Ensemble, à table, le pique-nique est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11845,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11543,7 +11874,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Au bac, Sara a les mains occupées. Elle a mangé assise, à table, ensemble. Maman dit : bravo d'être restée assise.</t>
+          <t>Au bac, Sara a les mains occupées. Elle a mangé assise, à table, ensemble. Bravo d'être restée assise.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11681,6 +12012,12 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Sara a les mains occupées. Elle a mangé assise, à table, ensemble.
+maman|Bravo d'être restée assise.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12206,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12375,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Le bac l'appelle.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12542,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12709,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Elle creuse. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12876,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13043,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Maman dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13210,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13377,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara gravit le toboggan. Avant, elle était assise à table, ensemble. Papa la voit.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13570,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13739,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Elle gravit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13906,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14073,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Papa la voit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14240,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14407,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Le toboggan attend. Maman range.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14574,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14741,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Aux balançoires, Sara chante. Elle a mangé assise, ensemble, à table. Maman plie la nappe.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14934,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15103,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Elle chante.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15270,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15437,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Maman plie.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15604,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15771,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. La nappe rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15938,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15603,6 +16055,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-011.xlsx
+++ b/stories/arbres/TREE-SAN-011.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Sara va au parc avec maman. Papa porte le panier. C'est l'heure de manger. On s'assoit. Assis à table, ensemble. Ici, la table est une nappe sur l'herbe. Sara pose les fesses. Elle reste assise.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1512,6 +1522,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1681,6 +1696,7 @@
           <t>narrateur|Un chat passe au loin. Sara s'assoit sur la nappe. Les fesses posées. Papa s'assoit. Maman s'assoit. Ils mangent ensemble, à table, sur la nappe. Sara reste assise.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1862,6 +1878,11 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Sara va manger au parc. Que fait-elle ?</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -2035,6 +2056,7 @@
           <t>narrateur|Sara est assise. La nappe est leur table. Ensemble, c'est calme. Le chat s'éloigne.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2252,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2421,7 @@
 maman|On a bien mangé assis.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2617,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2785,7 @@
           <t>narrateur|La nappe rouge est pliée. Sara a mangé assise à table, ensemble. Le bac l'attend.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2953,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3121,7 @@
           <t>narrateur|La nappe bleue sent l'herbe. Sara était assise. Ensemble, à table.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3289,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3457,7 @@
           <t>narrateur|La nappe verte a une miette. Sara a mangé assise, ensemble, à table.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3625,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3764,6 +3795,7 @@
 narrateur|Puis on glisse.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3959,6 +3991,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4126,6 +4159,7 @@
           <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Puis le toboggan.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4293,6 +4327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4460,6 +4495,7 @@
           <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Elle glisse.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4627,6 +4663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4794,6 +4831,7 @@
           <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Le toboggan attend.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4961,6 +4999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5128,6 +5167,7 @@
           <t>narrateur|Sara se balance après. Elle a d'abord mangé assise. À table, ensemble. Maman plie un coin de nappe.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5323,6 +5363,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5490,6 +5531,7 @@
           <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. La balançoire craque.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5657,6 +5699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5824,6 +5867,7 @@
           <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Elle se balance.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5991,6 +6035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6158,6 +6203,7 @@
           <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Maman plie.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6325,6 +6371,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6492,6 +6539,11 @@
           <t>narrateur|Le chien du parc reste avec son maître, loin. Sara s'assoit. Fesses sur la nappe. Papa et maman s'assoient. Ils mangent ensemble à table. Sara tient son sandwich. Elle reste assise.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc,chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6673,6 +6725,11 @@
       <c r="AW33" t="inlineStr">
         <is>
           <t>narrateur|Le chien est loin. Sara, elle, que fait-elle pour manger ?</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -6846,6 +6903,11 @@
           <t>narrateur|Sara est assise. Le chien ne vient pas. À table, ensemble, c'est le pique-nique.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7041,6 +7103,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7209,6 +7272,7 @@
 papa|D'abord on était assis.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7404,6 +7468,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7571,6 +7636,7 @@
           <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Le sable est tiède.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7738,6 +7804,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7905,6 +7972,7 @@
           <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Elle creuse.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8072,6 +8140,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8239,6 +8308,7 @@
           <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Papa garde le panier.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8406,6 +8476,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8573,6 +8644,7 @@
           <t>narrateur|Au toboggan, Sara attend son tour. Elle a mangé assise à table, ensemble. Maman range le panier.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8768,6 +8840,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8935,6 +9008,7 @@
           <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Elle attend.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9102,6 +9176,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9269,6 +9344,7 @@
           <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Le toboggan brille.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9436,6 +9512,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9603,6 +9680,7 @@
           <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Maman range.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9770,6 +9848,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9937,6 +10016,7 @@
           <t>narrateur|Sara se balance. Elle a d'abord été assise. À table, ensemble. Papa pousse tout doux.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10132,6 +10212,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10299,6 +10380,7 @@
           <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Ça va, ça vient.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10466,6 +10548,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10633,6 +10716,7 @@
           <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Papa pousse.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10800,6 +10884,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10967,6 +11052,7 @@
           <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Elle chante.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11134,6 +11220,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11301,6 +11388,7 @@
           <t>narrateur|Une poule du jardin d'à côté picore loin. Sara s'assoit à table, sur la nappe. Ensemble. Papa verse de l'eau. Maman ouvre la boîte. Sara mange assise. Les fesses bien posées.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11484,6 +11572,7 @@
           <t>narrateur|La poule picore. Sara, elle, que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11655,6 +11744,7 @@
           <t>narrateur|Sara est assise. La poule reste loin. Ensemble, à table, le pique-nique est calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11850,6 +11940,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12018,6 +12109,7 @@
 maman|Bravo d'être restée assise.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12213,6 +12305,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12380,6 +12473,7 @@
           <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Le bac l'appelle.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12547,6 +12641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12714,6 +12809,7 @@
           <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Elle creuse. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12881,6 +12977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13048,6 +13145,7 @@
           <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Maman dit merci.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13215,6 +13313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13382,6 +13481,7 @@
           <t>narrateur|Sara gravit le toboggan. Avant, elle était assise à table, ensemble. Papa la voit.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13577,6 +13677,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13744,6 +13845,7 @@
           <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Elle gravit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13911,6 +14013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14078,6 +14181,7 @@
           <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Papa la voit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14245,6 +14349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14412,6 +14517,7 @@
           <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. Le toboggan attend. Maman range.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14579,6 +14685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14746,6 +14853,7 @@
           <t>narrateur|Aux balançoires, Sara chante. Elle a mangé assise, ensemble, à table. Maman plie la nappe.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14941,6 +15049,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15108,6 +15217,7 @@
           <t>narrateur|Nappe rouge. Sara a mangé assise à table, ensemble. Elle chante.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15275,6 +15385,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15442,6 +15553,7 @@
           <t>narrateur|Nappe bleue. Sara était assise. Ensemble, à table. Maman plie.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15609,6 +15721,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15776,6 +15889,7 @@
           <t>narrateur|Nappe verte. Sara a mangé assise, ensemble, à table. La nappe rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15943,6 +16057,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15961,7 +16076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16062,6 +16177,20 @@
       <c r="A14" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16076,7 +16205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16263,6 +16392,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
